--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1-ballot</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:14:00+00:00</t>
+    <t>2024-03-29T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T13:28:39+00:00</t>
+    <t>2024-04-02T09:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:17:05+00:00</t>
+    <t>2024-04-02T09:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:24:51+00:00</t>
+    <t>2024-04-02T09:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T09:46:01+00:00</t>
+    <t>2024-04-02T14:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:06:21+00:00</t>
+    <t>2024-04-02T14:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T09:39:19+00:00</t>
+    <t>2024-06-10T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T12:17:15+00:00</t>
+    <t>2024-06-11T12:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:10:45+00:00</t>
+    <t>2024-06-11T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T12:11:06+00:00</t>
+    <t>2024-06-14T08:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:12:27+00:00</t>
+    <t>2024-06-14T08:15:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T08:15:01+00:00</t>
+    <t>2024-06-19T07:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-19T07:50:19+00:00</t>
+    <t>2024-06-20T09:03:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-20T09:03:18+00:00</t>
+    <t>2024-06-26T16:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T16:31:19+00:00</t>
+    <t>2024-07-24T15:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T15:57:10+00:00</t>
+    <t>2024-07-25T10:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T10:14:34+00:00</t>
+    <t>2024-07-31T08:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="313">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T08:54:42+00:00</t>
+    <t>2024-09-06T13:26:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,10 +316,6 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -343,9 +339,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -388,12 +381,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -474,8 +461,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-1</t>
+    <t xml:space="preserve">bdl-1
+</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -512,6 +499,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -532,16 +522,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -578,9 +558,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -588,9 +565,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -609,8 +583,11 @@
     <t>Slicing based on the profile conformance of the entry</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>open</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -659,9 +636,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -671,8 +645,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -728,8 +702,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -783,9 +757,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -813,8 +784,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1361,8 +1332,8 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="62.87890625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="143.74609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="50.08203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
@@ -1809,16 +1780,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1829,10 +1800,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1855,16 +1826,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1914,7 +1885,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1923,16 +1894,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1943,10 +1914,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1969,16 +1940,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2004,32 +1975,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2037,16 +2008,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2057,10 +2028,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2083,16 +2054,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2142,7 +2113,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2151,30 +2122,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2197,16 +2168,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2217,78 +2188,78 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2311,16 +2282,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2370,7 +2341,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2379,30 +2350,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2425,16 +2396,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2484,7 +2455,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2493,16 +2464,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2513,10 +2484,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2539,16 +2510,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2598,7 +2569,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2607,16 +2578,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2627,10 +2598,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2653,13 +2624,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2710,7 +2681,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2728,7 +2699,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2739,14 +2710,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2765,16 +2736,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2812,19 +2783,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2833,16 +2804,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2853,14 +2824,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2879,19 +2850,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2940,7 +2911,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2949,10 +2920,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -2969,10 +2940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2995,17 +2966,15 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3054,7 +3023,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3063,16 +3032,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3083,10 +3052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3109,17 +3078,15 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3168,7 +3135,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3177,16 +3144,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3197,10 +3164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3223,13 +3190,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3268,19 +3235,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3289,16 +3256,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3309,10 +3276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3335,13 +3302,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3392,7 +3359,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3410,7 +3377,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3421,14 +3388,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3447,16 +3414,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3494,19 +3461,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3515,16 +3482,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3535,14 +3502,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3561,19 +3528,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3622,7 +3589,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3631,10 +3598,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3651,10 +3618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3680,10 +3647,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3734,7 +3701,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3746,7 +3713,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3763,10 +3730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3789,16 +3756,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3848,7 +3815,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3857,16 +3824,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3877,10 +3844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3903,13 +3870,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3960,7 +3927,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3978,7 +3945,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3989,10 +3956,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4015,13 +3982,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4072,7 +4039,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4081,16 +4048,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4101,10 +4068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4127,13 +4094,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4184,7 +4151,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4202,7 +4169,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4213,14 +4180,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4239,16 +4206,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4286,19 +4253,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4307,16 +4274,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4327,14 +4294,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4353,19 +4320,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4414,7 +4381,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4423,10 +4390,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4443,10 +4410,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4469,16 +4436,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4504,13 +4471,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4528,7 +4495,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4537,16 +4504,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4557,10 +4524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4583,16 +4550,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4642,7 +4609,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4651,16 +4618,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4671,10 +4638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4697,13 +4664,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4754,7 +4721,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4763,16 +4730,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4783,10 +4750,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4809,13 +4776,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4866,7 +4833,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4884,7 +4851,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4895,14 +4862,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4921,16 +4888,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4968,19 +4935,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4989,16 +4956,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5009,14 +4976,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5035,19 +5002,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5096,7 +5063,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5105,10 +5072,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5125,10 +5092,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5151,17 +5118,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5186,13 +5151,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5210,7 +5175,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5219,16 +5184,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5239,10 +5204,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5265,16 +5230,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5324,7 +5289,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5333,16 +5298,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5353,10 +5318,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5379,17 +5344,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5438,7 +5401,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5447,16 +5410,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5467,10 +5430,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5493,17 +5456,15 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5552,7 +5513,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5561,16 +5522,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5581,10 +5542,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5607,17 +5568,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5666,7 +5625,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5675,16 +5634,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5695,10 +5654,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5721,17 +5680,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5780,7 +5737,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5789,16 +5746,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5809,10 +5766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5835,13 +5792,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5892,7 +5849,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5901,16 +5858,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5921,10 +5878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5947,13 +5904,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6004,7 +5961,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6022,7 +5979,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6033,14 +5990,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6059,16 +6016,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6106,19 +6063,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6127,16 +6084,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6147,14 +6104,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6173,19 +6130,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6234,7 +6191,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6243,10 +6200,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6263,10 +6220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6289,17 +6246,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6348,7 +6303,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6357,16 +6312,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6377,10 +6332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6403,17 +6358,15 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6462,7 +6415,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6471,16 +6424,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6491,10 +6444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6517,16 +6470,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6576,7 +6529,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6585,16 +6538,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6605,10 +6558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6631,16 +6584,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6690,7 +6643,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6699,16 +6652,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6719,10 +6672,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6745,16 +6698,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6804,7 +6757,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6822,7 +6775,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6833,13 +6786,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6861,13 +6814,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6918,7 +6871,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6927,16 +6880,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6947,10 +6900,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6973,13 +6926,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7030,7 +6983,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7048,7 +7001,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7059,14 +7012,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7085,16 +7038,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7132,19 +7085,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7153,16 +7106,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7173,14 +7126,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7199,19 +7152,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7260,7 +7213,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7269,10 +7222,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7289,10 +7242,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7318,10 +7271,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7372,7 +7325,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7384,7 +7337,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7401,10 +7354,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7427,16 +7380,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7486,7 +7439,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7495,16 +7448,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7515,10 +7468,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7541,16 +7494,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7600,7 +7553,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7618,10 +7571,10 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7629,10 +7582,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7655,13 +7608,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7712,7 +7665,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7721,16 +7674,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7741,10 +7694,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7767,13 +7720,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7824,7 +7777,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7842,7 +7795,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7853,14 +7806,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7879,16 +7832,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7926,19 +7879,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7947,16 +7900,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -7967,14 +7920,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7993,19 +7946,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8054,7 +8007,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8063,10 +8016,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8083,10 +8036,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8109,16 +8062,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8144,13 +8097,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8168,7 +8121,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8177,16 +8130,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8197,10 +8150,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8223,16 +8176,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8282,7 +8235,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8291,16 +8244,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8311,10 +8264,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8337,13 +8290,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8394,7 +8347,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8403,16 +8356,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8423,10 +8376,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8449,13 +8402,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8506,7 +8459,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8524,7 +8477,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8535,14 +8488,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8561,16 +8514,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8608,19 +8561,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8629,16 +8582,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8649,14 +8602,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8675,19 +8628,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8736,7 +8689,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8745,10 +8698,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8765,10 +8718,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8791,17 +8744,15 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8811,7 +8762,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -8826,13 +8777,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8850,7 +8801,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8859,16 +8810,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8879,10 +8830,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8905,16 +8856,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8964,7 +8915,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -8973,16 +8924,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -8993,10 +8944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9019,17 +8970,15 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9078,7 +9027,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9087,16 +9036,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9107,10 +9056,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9133,17 +9082,15 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9192,7 +9139,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9201,16 +9148,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9221,10 +9168,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9247,17 +9194,15 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9306,7 +9251,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9315,16 +9260,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9335,10 +9280,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9361,17 +9306,15 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9420,7 +9363,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9429,16 +9372,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9449,10 +9392,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9475,13 +9418,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9532,7 +9475,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9541,16 +9484,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9561,10 +9504,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9587,13 +9530,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9644,7 +9587,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9662,7 +9605,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9673,14 +9616,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9699,16 +9642,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9746,19 +9689,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9767,16 +9710,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9787,14 +9730,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9813,19 +9756,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9874,7 +9817,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9883,10 +9826,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9903,10 +9846,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9929,17 +9872,15 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -9988,7 +9929,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -9997,16 +9938,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10017,10 +9958,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10043,17 +9984,15 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10102,7 +10041,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10111,16 +10050,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10131,10 +10070,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10157,16 +10096,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10216,7 +10155,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10225,16 +10164,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10245,10 +10184,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10271,16 +10210,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10330,7 +10269,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10339,16 +10278,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10359,10 +10298,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10385,16 +10324,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10444,7 +10383,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10462,7 +10401,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10473,10 +10412,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10499,19 +10438,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10560,7 +10499,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10569,16 +10508,16 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T13:26:49+00:00</t>
+    <t>2024-09-23T13:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -619,7 +619,7 @@
 * Results from operations might involve resources that are not identified.</t>
   </si>
   <si>
-    <t>fullUrl might not be [unique in the context of a resource](bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
+    <t>fullUrl might not be [unique in the context of a resource](http://hl7.org/fhir/R4/bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
 Note that the fullUrl is not the same as the canonical URL - it's an absolute url for an endpoint serving the resource (these will happen to have the same value on the canonical server for the resource with the canonical URL).</t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T13:29:51+00:00</t>
+    <t>2024-09-24T15:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T15:02:27+00:00</t>
+    <t>2024-09-25T14:04:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T14:04:17+00:00</t>
+    <t>2024-10-02T09:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T09:58:03+00:00</t>
+    <t>2026-01-26T12:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T12:56:49+00:00</t>
+    <t>2026-02-05T13:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Bundle|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Bundle</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -883,7 +883,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot}
+    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient}
 </t>
   </si>
   <si>
@@ -1004,7 +1004,7 @@
     <t>Bundle.entry:DUIPatientINS.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot}
+    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins}
 </t>
   </si>
   <si>
@@ -1110,7 +1110,7 @@
     <t>Bundle.entry:DUIOrganization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization|2.2.0-ballot}
+    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization}
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-sejour|2.2.0-ballot}
+    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-sejour}
 </t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>Bundle.entry:DUIEncounterEvenement.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement|2.2.0-ballot}
+    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement}
 </t>
   </si>
   <si>
@@ -1453,7 +1453,7 @@
     <t>Bundle.entry:DUIPractitioner.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot}
+    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner}
 </t>
   </si>
   <si>
@@ -1571,7 +1571,7 @@
     <t>Bundle.entry:DUIPractitionerRole.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|2.2.0-ballot}
+    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role}
 </t>
   </si>
   <si>
@@ -1683,7 +1683,7 @@
     <t>Bundle.entry:DUITransportProfessionnel.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport-professionnel|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport-professionnel}
 </t>
   </si>
   <si>
@@ -1798,7 +1798,7 @@
     <t>Bundle.entry:DUITransportUsager.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport-usager|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport-usager}
 </t>
   </si>
   <si>
@@ -1904,7 +1904,7 @@
     <t>Bundle.entry:DUIDocumentReference.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-document-reference|2.2.0-ballot}
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-document-reference}
 </t>
   </si>
   <si>
@@ -2029,7 +2029,7 @@
 QuestionnaireAnswers</t>
   </si>
   <si>
-    <t xml:space="preserve">QuestionnaireResponse {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-questionnaire-response|2.2.0-ballot}
+    <t xml:space="preserve">QuestionnaireResponse {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-questionnaire-response}
 </t>
   </si>
   <si>
@@ -2151,7 +2151,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CarePlan {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-projet-personnalise|2.2.0-ballot}
+    <t xml:space="preserve">CarePlan {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-projet-personnalise}
 </t>
   </si>
   <si>
@@ -2266,7 +2266,7 @@
     <t>Bundle.entry:DUIConsentAccord.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Consent {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-consent-accord|2.2.0-ballot}
+    <t xml:space="preserve">Consent {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-consent-accord}
 </t>
   </si>
   <si>
@@ -2387,7 +2387,7 @@
     <t>Bundle.entry:DUIGoalAttente.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-goal-attente|2.2.0-ballot}
+    <t xml:space="preserve">Goal {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-goal-attente}
 </t>
   </si>
   <si>
@@ -2508,7 +2508,7 @@
     <t>Bundle.entry:DUIGoalObjectif.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-goal-objectif|2.2.0-ballot}
+    <t xml:space="preserve">Goal {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-goal-objectif}
 </t>
   </si>
   <si>
@@ -2618,7 +2618,7 @@
 referralreferral requesttransfer of care request</t>
   </si>
   <si>
-    <t xml:space="preserve">ServiceRequest {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin|2.2.0-ballot}
+    <t xml:space="preserve">ServiceRequest {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin}
 </t>
   </si>
   <si>
@@ -2736,7 +2736,7 @@
     <t>Bundle.entry:DUITaskAction.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-action|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-action}
 </t>
   </si>
   <si>
@@ -2842,7 +2842,7 @@
     <t>Bundle.entry:DUITaskBilan.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-bilan|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-bilan}
 </t>
   </si>
   <si>
@@ -2948,7 +2948,7 @@
     <t>Bundle.entry:DUITaskMoyenRessource.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-moyen-ressource|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-moyen-ressource}
 </t>
   </si>
   <si>
@@ -3054,7 +3054,7 @@
     <t>Bundle.entry:DUITaskPrestation.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-prestation|2.2.0-ballot}
+    <t xml:space="preserve">Task {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-prestation}
 </t>
   </si>
   <si>
@@ -3160,7 +3160,7 @@
     <t>Bundle.entry:RelatedPerson.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.1.0}
+    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person}
 </t>
   </si>
   <si>
@@ -3579,7 +3579,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="103.59765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:38:35+00:00</t>
+    <t>2026-02-05T14:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3133,34 +3133,34 @@
     <t>Bundle.entry:DUITaskPrestation.response.outcome</t>
   </si>
   <si>
-    <t>Bundle.entry:RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson conforming to the FrCoreRelatedPerson profile, used to convey information about the user's contacts.</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person}
+    <t>Bundle.entry:DUIRelatedPersonContact</t>
+  </si>
+  <si>
+    <t>DUIRelatedPersonContact</t>
+  </si>
+  <si>
+    <t>RelatedPerson conforming to the TDDUIRelatedPersonContact profile, used to convey information about the contact person.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedPerson {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact}
 </t>
   </si>
   <si>
@@ -3173,79 +3173,79 @@
     <t>role</t>
   </si>
   <si>
-    <t>Bundle.entry:RelatedPerson.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.outcome</t>
+    <t>Bundle.entry:DUIRelatedPersonContact.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:50:20+00:00</t>
+    <t>2026-02-05T15:15:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/main/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
